--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1393093-1692-CM25</t>
+          <t>3479-1655-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12212.49</v>
+        <v>2069.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>387-792-CM25</t>
+          <t>1393093-1692-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8877.4</v>
+        <v>12212.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2989-849-CM25</t>
+          <t>387-792-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5680.01</v>
+        <v>8877.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3443-1047-CM25</t>
+          <t>2989-849-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10651.45</v>
+        <v>5680.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>387-72-CM26</t>
+          <t>3443-1047-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>845.52</v>
+        <v>10651.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>387-72-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4435.13</v>
+        <v>845.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3443-351-CM26</t>
+          <t>2912-80-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Departamento Administrativo de Salud Municipal.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5094.26</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3507-326-CM26</t>
+          <t>3443-351-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17740.52</v>
+        <v>5094.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3479-1041-CM26</t>
+          <t>3507-326-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15946</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3479-1147-CM26</t>
+          <t>3479-1041-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,6 +1118,67 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>15946</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3479-1147-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>7923.26</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3479-1655-CM25</t>
+          <t>2912-1686-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2069.65</v>
+        <v>1154.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1393093-1692-CM25</t>
+          <t>2989-190-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12212.49</v>
+        <v>4283.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>387-792-CM25</t>
+          <t>2854-333-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8877.4</v>
+        <v>35893.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2989-849-CM25</t>
+          <t>752-174-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5680.01</v>
+        <v>10575.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3443-1047-CM25</t>
+          <t>3507-332-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10651.45</v>
+        <v>15091.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>387-72-CM26</t>
+          <t>2332-472-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>845.52</v>
+        <v>1284.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>2332-665-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4435.13</v>
+        <v>4283.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3443-351-CM26</t>
+          <t>752-374-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5094.26</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3507-326-CM26</t>
+          <t>3479-1655-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17740.52</v>
+        <v>2069.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3479-1041-CM26</t>
+          <t>1393093-1692-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15946</v>
+        <v>12212.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3479-1147-CM26</t>
+          <t>2989-849-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,6 +1179,494 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
+        <v>5680.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>387-792-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.220.800-5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>8877.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3443-1047-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.210.500-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>10651.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>387-72-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.220.800-5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>845.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2912-80-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.220.702-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Departamento Administrativo de Salud Municipal.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>4435.13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3443-351-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.210.500-1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>5094.26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3507-326-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>65.321.890-7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Departamento de Salud</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>17740.52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3479-1041-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>15946</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3479-1147-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>7923.26</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2912-80-CM26</t>
+          <t>1237404-18-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>65.293.750-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE ANCUD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4435.13</v>
+        <v>1846.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3443-351-CM26</t>
+          <t>2912-80-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5094.26</v>
+        <v>4435.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3507-326-CM26</t>
+          <t>1456840-17-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17740.52</v>
+        <v>1173.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3479-1041-CM26</t>
+          <t>3443-351-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15946</v>
+        <v>5094.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3479-1147-CM26</t>
+          <t>3507-326-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,6 +1667,128 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
+        <v>17740.52</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3479-1041-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>15946</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3479-1147-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>7923.26</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-lagos.xlsx
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
